--- a/data/raw_data/dataset.xlsx
+++ b/data/raw_data/dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MSc Data Science\Machine Learning\CourseWork\Q_03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MSc Data Science\Machine Learning\CourseWork\Q_03\retail-workforce-shift-optimization\retail-workforce-shift-optimization\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B73C713-5C6D-479C-8CB7-44C78F7DBB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAF6A4E-3642-4DB7-83AE-020B5E832748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7744B7AA-827D-4A73-9E53-433638A858A9}"/>
   </bookViews>
@@ -840,6 +840,9 @@
       </filters>
     </filterColumn>
   </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A58:L151">
+    <sortCondition ref="K1:K201"/>
+  </sortState>
   <tableColumns count="12">
     <tableColumn id="2" xr3:uid="{5F8F8EFD-85CD-42A6-A289-D650CCE2FDF0}" uniqueName="2" name="employee_id" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{AC8158A8-E117-4A23-A2FB-A5697A7D1207}" uniqueName="3" name="employee_name" queryTableFieldId="3" dataDxfId="8"/>
@@ -3314,7 +3317,7 @@
         <v>45479</v>
       </c>
       <c r="K56" s="2">
-        <v>45479.291666666664</v>
+        <v>45479.208333333336</v>
       </c>
       <c r="L56" s="2">
         <v>45479.666666666664</v>
@@ -3360,78 +3363,78 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>127</v>
+        <v>1503</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D58" s="1">
-        <v>45480</v>
+        <v>45474</v>
       </c>
       <c r="E58" s="2">
-        <v>45480.625</v>
+        <v>45474.25</v>
       </c>
       <c r="F58" s="2">
-        <v>45480.875</v>
+        <v>45474.5</v>
       </c>
       <c r="G58">
         <v>6</v>
       </c>
       <c r="H58">
-        <v>15</v>
+        <v>16.25</v>
       </c>
       <c r="I58" t="s">
         <v>78</v>
       </c>
       <c r="J58" s="1">
-        <v>45480</v>
+        <v>45474</v>
       </c>
       <c r="K58" s="2">
-        <v>45480.583333333336</v>
+        <v>45474.229166666664</v>
       </c>
       <c r="L58" s="2">
-        <v>45480.916666666664</v>
+        <v>45474.541666666664</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>128</v>
+        <v>1501</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D59" s="1">
-        <v>45480</v>
+        <v>45474</v>
       </c>
       <c r="E59" s="2">
-        <v>45480.416666666664</v>
+        <v>45474.333333333336</v>
       </c>
       <c r="F59" s="2">
-        <v>45480.75</v>
+        <v>45474.583333333336</v>
       </c>
       <c r="G59">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H59">
-        <v>17</v>
+        <v>14.75</v>
       </c>
       <c r="I59" t="s">
         <v>78</v>
       </c>
       <c r="J59" s="1">
-        <v>45480</v>
+        <v>45474</v>
       </c>
       <c r="K59" s="2">
-        <v>45480.375</v>
+        <v>45474.3125</v>
       </c>
       <c r="L59" s="2">
-        <v>45480.791666666664</v>
+        <v>45474.625</v>
       </c>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3466,7 +3469,7 @@
         <v>45481</v>
       </c>
       <c r="K60" s="2">
-        <v>45481.333333333336</v>
+        <v>45481.208333333336</v>
       </c>
       <c r="L60" s="2">
         <v>45481.708333333336</v>
@@ -3504,7 +3507,7 @@
         <v>45481</v>
       </c>
       <c r="K61" s="2">
-        <v>45481.4375</v>
+        <v>45481.229166666664</v>
       </c>
       <c r="L61" s="2">
         <v>45481.8125</v>
@@ -3580,7 +3583,7 @@
         <v>45482</v>
       </c>
       <c r="K63" s="2">
-        <v>45482.333333333336</v>
+        <v>45482.208333333336</v>
       </c>
       <c r="L63" s="2">
         <v>45482.666666666664</v>
@@ -3588,40 +3591,40 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>133</v>
+        <v>1502</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="C64" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D64" s="1">
-        <v>45483</v>
+        <v>45474</v>
       </c>
       <c r="E64" s="2">
-        <v>45483.583333333336</v>
+        <v>45474.375</v>
       </c>
       <c r="F64" s="2">
-        <v>45483.833333333336</v>
+        <v>45474.75</v>
       </c>
       <c r="G64">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H64">
-        <v>13.25</v>
+        <v>28.5</v>
       </c>
       <c r="I64" t="s">
         <v>78</v>
       </c>
       <c r="J64" s="1">
-        <v>45483</v>
+        <v>45474</v>
       </c>
       <c r="K64" s="2">
-        <v>45483.541666666664</v>
+        <v>45474.354166666664</v>
       </c>
       <c r="L64" s="2">
-        <v>45483.875</v>
+        <v>45474.770833333336</v>
       </c>
     </row>
     <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3656,7 +3659,7 @@
         <v>45483</v>
       </c>
       <c r="K65" s="2">
-        <v>45483.3125</v>
+        <v>45483.229166666664</v>
       </c>
       <c r="L65" s="2">
         <v>45483.583333333336</v>
@@ -3694,7 +3697,7 @@
         <v>45484</v>
       </c>
       <c r="K66" s="2">
-        <v>45484.354166666664</v>
+        <v>45484.229166666664</v>
       </c>
       <c r="L66" s="2">
         <v>45484.729166666664</v>
@@ -3702,40 +3705,40 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>136</v>
+        <v>1504</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C67" t="s">
         <v>18</v>
       </c>
       <c r="D67" s="1">
-        <v>45484</v>
+        <v>45474</v>
       </c>
       <c r="E67" s="2">
-        <v>45484.666666666664</v>
+        <v>45474.5</v>
       </c>
       <c r="F67" s="2">
-        <v>45484.916666666664</v>
+        <v>45474.75</v>
       </c>
       <c r="G67">
         <v>6</v>
       </c>
       <c r="H67">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="I67" t="s">
         <v>78</v>
       </c>
       <c r="J67" s="1">
-        <v>45484</v>
+        <v>45474</v>
       </c>
       <c r="K67" s="2">
-        <v>45484.625</v>
+        <v>45474.229166666664</v>
       </c>
       <c r="L67" s="2">
-        <v>45484.958333333336</v>
+        <v>45474.791666666664</v>
       </c>
     </row>
     <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3770,7 +3773,7 @@
         <v>45485</v>
       </c>
       <c r="K68" s="2">
-        <v>45485.291666666664</v>
+        <v>45485.208333333336</v>
       </c>
       <c r="L68" s="2">
         <v>45485.666666666664</v>
@@ -3846,7 +3849,7 @@
         <v>45486</v>
       </c>
       <c r="K70" s="2">
-        <v>45486.666666666664</v>
+        <v>45486.208333333336</v>
       </c>
       <c r="L70" s="2">
         <v>45486.916666666664</v>
@@ -3854,40 +3857,40 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>140</v>
+        <v>1505</v>
       </c>
       <c r="B71" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D71" s="1">
-        <v>45486</v>
+        <v>45474</v>
       </c>
       <c r="E71" s="2">
-        <v>45486.375</v>
+        <v>45474.583333333336</v>
       </c>
       <c r="F71" s="2">
-        <v>45486.708333333336</v>
+        <v>45474.916666666664</v>
       </c>
       <c r="G71">
         <v>8</v>
       </c>
       <c r="H71">
-        <v>16.75</v>
+        <v>22</v>
       </c>
       <c r="I71" t="s">
         <v>78</v>
       </c>
       <c r="J71" s="1">
-        <v>45486</v>
+        <v>45474</v>
       </c>
       <c r="K71" s="2">
-        <v>45486.333333333336</v>
+        <v>45474.5625</v>
       </c>
       <c r="L71" s="2">
-        <v>45486.729166666664</v>
+        <v>45474.9375</v>
       </c>
     </row>
     <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3922,7 +3925,7 @@
         <v>45487</v>
       </c>
       <c r="K72" s="2">
-        <v>45487.479166666664</v>
+        <v>45487.229166666664</v>
       </c>
       <c r="L72" s="2">
         <v>45487.854166666664</v>
@@ -3930,78 +3933,78 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>142</v>
+        <v>1508</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
         <v>20</v>
       </c>
       <c r="D73" s="1">
-        <v>45487</v>
+        <v>45475</v>
       </c>
       <c r="E73" s="2">
-        <v>45487.333333333336</v>
+        <v>45475.208333333336</v>
       </c>
       <c r="F73" s="2">
-        <v>45487.583333333336</v>
+        <v>45475.541666666664</v>
       </c>
       <c r="G73">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H73">
-        <v>13</v>
+        <v>16.75</v>
       </c>
       <c r="I73" t="s">
         <v>78</v>
       </c>
       <c r="J73" s="1">
-        <v>45487</v>
+        <v>45475</v>
       </c>
       <c r="K73" s="2">
-        <v>45487.3125</v>
+        <v>45475.1875</v>
       </c>
       <c r="L73" s="2">
-        <v>45487.604166666664</v>
+        <v>45475.5625</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>143</v>
+        <v>1506</v>
       </c>
       <c r="B74" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="C74" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D74" s="1">
-        <v>45488</v>
+        <v>45475</v>
       </c>
       <c r="E74" s="2">
-        <v>45488.583333333336</v>
+        <v>45475.333333333336</v>
       </c>
       <c r="F74" s="2">
-        <v>45488.916666666664</v>
+        <v>45475.666666666664</v>
       </c>
       <c r="G74">
         <v>8</v>
       </c>
       <c r="H74">
-        <v>21.75</v>
+        <v>15</v>
       </c>
       <c r="I74" t="s">
         <v>78</v>
       </c>
       <c r="J74" s="1">
-        <v>45488</v>
+        <v>45475</v>
       </c>
       <c r="K74" s="2">
-        <v>45488.541666666664</v>
+        <v>45475.3125</v>
       </c>
       <c r="L74" s="2">
-        <v>45488.958333333336</v>
+        <v>45475.6875</v>
       </c>
     </row>
     <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4044,40 +4047,40 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>145</v>
+        <v>1507</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="C76" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D76" s="1">
-        <v>45489</v>
+        <v>45475</v>
       </c>
       <c r="E76" s="2">
-        <v>45489.458333333336</v>
+        <v>45475.416666666664</v>
       </c>
       <c r="F76" s="2">
-        <v>45489.666666666664</v>
+        <v>45475.75</v>
       </c>
       <c r="G76">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H76">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I76" t="s">
         <v>78</v>
       </c>
       <c r="J76" s="1">
-        <v>45489</v>
+        <v>45475</v>
       </c>
       <c r="K76" s="2">
-        <v>45489.4375</v>
+        <v>45475.229166666664</v>
       </c>
       <c r="L76" s="2">
-        <v>45489.6875</v>
+        <v>45475.770833333336</v>
       </c>
     </row>
     <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4112,7 +4115,7 @@
         <v>45489</v>
       </c>
       <c r="K77" s="2">
-        <v>45489.3125</v>
+        <v>45489.479166666664</v>
       </c>
       <c r="L77" s="2">
         <v>45489.625</v>
@@ -4120,28 +4123,28 @@
     </row>
     <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D78" s="1">
         <v>45490</v>
       </c>
       <c r="E78" s="2">
-        <v>45490.541666666664</v>
+        <v>45490.333333333336</v>
       </c>
       <c r="F78" s="2">
-        <v>45490.875</v>
+        <v>45490.666666666664</v>
       </c>
       <c r="G78">
         <v>8</v>
       </c>
       <c r="H78">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I78" t="s">
         <v>70</v>
@@ -4150,36 +4153,36 @@
         <v>45490</v>
       </c>
       <c r="K78" s="2">
-        <v>45490.520833333336</v>
+        <v>45490.479166666664</v>
       </c>
       <c r="L78" s="2">
-        <v>45490.895833333336</v>
+        <v>45490.6875</v>
       </c>
     </row>
     <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D79" s="1">
         <v>45490</v>
       </c>
       <c r="E79" s="2">
-        <v>45490.333333333336</v>
+        <v>45490.541666666664</v>
       </c>
       <c r="F79" s="2">
-        <v>45490.666666666664</v>
+        <v>45490.875</v>
       </c>
       <c r="G79">
         <v>8</v>
       </c>
       <c r="H79">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I79" t="s">
         <v>70</v>
@@ -4188,10 +4191,10 @@
         <v>45490</v>
       </c>
       <c r="K79" s="2">
-        <v>45490.3125</v>
+        <v>45490.479166666664</v>
       </c>
       <c r="L79" s="2">
-        <v>45490.6875</v>
+        <v>45490.895833333336</v>
       </c>
     </row>
     <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4264,7 +4267,7 @@
         <v>45491</v>
       </c>
       <c r="K81" s="2">
-        <v>45491.583333333336</v>
+        <v>45491.479166666664</v>
       </c>
       <c r="L81" s="2">
         <v>45491.958333333336</v>
@@ -4272,78 +4275,78 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>151</v>
+        <v>1509</v>
       </c>
       <c r="B82" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="C82" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D82" s="1">
-        <v>45492</v>
+        <v>45475</v>
       </c>
       <c r="E82" s="2">
-        <v>45492.375</v>
+        <v>45475.583333333336</v>
       </c>
       <c r="F82" s="2">
-        <v>45492.625</v>
+        <v>45475.916666666664</v>
       </c>
       <c r="G82">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H82">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="I82" t="s">
         <v>78</v>
       </c>
       <c r="J82" s="1">
-        <v>45492</v>
+        <v>45475</v>
       </c>
       <c r="K82" s="2">
-        <v>45492.354166666664</v>
+        <v>45475.5625</v>
       </c>
       <c r="L82" s="2">
-        <v>45492.666666666664</v>
+        <v>45475.9375</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>152</v>
+        <v>1510</v>
       </c>
       <c r="B83" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="C83" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D83" s="1">
-        <v>45492</v>
+        <v>45475</v>
       </c>
       <c r="E83" s="2">
-        <v>45492.541666666664</v>
+        <v>45475.666666666664</v>
       </c>
       <c r="F83" s="2">
-        <v>45492.875</v>
+        <v>45475.958333333336</v>
       </c>
       <c r="G83">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H83">
-        <v>16.75</v>
+        <v>23.5</v>
       </c>
       <c r="I83" t="s">
         <v>78</v>
       </c>
       <c r="J83" s="1">
-        <v>45492</v>
+        <v>45475</v>
       </c>
       <c r="K83" s="2">
-        <v>45492.520833333336</v>
+        <v>45475.645833333336</v>
       </c>
       <c r="L83" s="2">
-        <v>45492.895833333336</v>
+        <v>45475.979166666664</v>
       </c>
     </row>
     <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4378,7 +4381,7 @@
         <v>45493</v>
       </c>
       <c r="K84" s="2">
-        <v>45493.3125</v>
+        <v>45493.229166666664</v>
       </c>
       <c r="L84" s="2">
         <v>45493.604166666664</v>
@@ -4492,7 +4495,7 @@
         <v>45494</v>
       </c>
       <c r="K87" s="2">
-        <v>45494.5625</v>
+        <v>45494.229166666664</v>
       </c>
       <c r="L87" s="2">
         <v>45494.854166666664</v>
@@ -4500,78 +4503,78 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>157</v>
+        <v>1513</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C88" t="s">
         <v>20</v>
       </c>
       <c r="D88" s="1">
-        <v>45495</v>
+        <v>45476</v>
       </c>
       <c r="E88" s="2">
-        <v>45495.354166666664</v>
+        <v>45476.25</v>
       </c>
       <c r="F88" s="2">
-        <v>45495.604166666664</v>
+        <v>45476.5</v>
       </c>
       <c r="G88">
         <v>6</v>
       </c>
       <c r="H88">
-        <v>13.75</v>
+        <v>16.5</v>
       </c>
       <c r="I88" t="s">
         <v>78</v>
       </c>
       <c r="J88" s="1">
-        <v>45495</v>
+        <v>45476</v>
       </c>
       <c r="K88" s="2">
-        <v>45495.333333333336</v>
+        <v>45476.229166666664</v>
       </c>
       <c r="L88" s="2">
-        <v>45495.625</v>
+        <v>45476.541666666664</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>158</v>
+        <v>1511</v>
       </c>
       <c r="B89" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C89" t="s">
         <v>13</v>
       </c>
       <c r="D89" s="1">
-        <v>45495</v>
+        <v>45476</v>
       </c>
       <c r="E89" s="2">
-        <v>45495.541666666664</v>
+        <v>45476.291666666664</v>
       </c>
       <c r="F89" s="2">
-        <v>45495.791666666664</v>
+        <v>45476.541666666664</v>
       </c>
       <c r="G89">
         <v>6</v>
       </c>
       <c r="H89">
-        <v>15.5</v>
+        <v>15.25</v>
       </c>
       <c r="I89" t="s">
         <v>78</v>
       </c>
       <c r="J89" s="1">
-        <v>45495</v>
+        <v>45476</v>
       </c>
       <c r="K89" s="2">
-        <v>45495.520833333336</v>
+        <v>45476.270833333336</v>
       </c>
       <c r="L89" s="2">
-        <v>45495.8125</v>
+        <v>45476.5625</v>
       </c>
     </row>
     <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4606,7 +4609,7 @@
         <v>45496</v>
       </c>
       <c r="K90" s="2">
-        <v>45496.354166666664</v>
+        <v>45496.5625</v>
       </c>
       <c r="L90" s="2">
         <v>45496.729166666664</v>
@@ -4644,7 +4647,7 @@
         <v>45496</v>
       </c>
       <c r="K91" s="2">
-        <v>45496.520833333336</v>
+        <v>45496.5625</v>
       </c>
       <c r="L91" s="2">
         <v>45496.895833333336</v>
@@ -4682,7 +4685,7 @@
         <v>45497</v>
       </c>
       <c r="K92" s="2">
-        <v>45497.4375</v>
+        <v>45497.5625</v>
       </c>
       <c r="L92" s="2">
         <v>45497.6875</v>
@@ -4690,40 +4693,40 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>162</v>
+        <v>1512</v>
       </c>
       <c r="B93" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C93" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D93" s="1">
-        <v>45497</v>
+        <v>45476</v>
       </c>
       <c r="E93" s="2">
-        <v>45497.375</v>
+        <v>45476.375</v>
       </c>
       <c r="F93" s="2">
-        <v>45497.625</v>
+        <v>45476.75</v>
       </c>
       <c r="G93">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H93">
-        <v>15.75</v>
+        <v>27.75</v>
       </c>
       <c r="I93" t="s">
         <v>78</v>
       </c>
       <c r="J93" s="1">
-        <v>45497</v>
+        <v>45476</v>
       </c>
       <c r="K93" s="2">
-        <v>45497.354166666664</v>
+        <v>45476.229166666664</v>
       </c>
       <c r="L93" s="2">
-        <v>45497.645833333336</v>
+        <v>45476.770833333336</v>
       </c>
     </row>
     <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4758,7 +4761,7 @@
         <v>45498</v>
       </c>
       <c r="K94" s="2">
-        <v>45498.6875</v>
+        <v>45498.5625</v>
       </c>
       <c r="L94" s="2">
         <v>45498.9375</v>
@@ -4872,7 +4875,7 @@
         <v>45499</v>
       </c>
       <c r="K97" s="2">
-        <v>45499.479166666664</v>
+        <v>45499.5625</v>
       </c>
       <c r="L97" s="2">
         <v>45499.854166666664</v>
@@ -4880,25 +4883,25 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>167</v>
+        <v>1514</v>
       </c>
       <c r="B98" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C98" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D98" s="1">
-        <v>45500</v>
+        <v>45476</v>
       </c>
       <c r="E98" s="2">
-        <v>45500.625</v>
+        <v>45476.5</v>
       </c>
       <c r="F98" s="2">
-        <v>45500.916666666664</v>
+        <v>45476.75</v>
       </c>
       <c r="G98">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H98">
         <v>18</v>
@@ -4907,77 +4910,77 @@
         <v>78</v>
       </c>
       <c r="J98" s="1">
-        <v>45500</v>
+        <v>45476</v>
       </c>
       <c r="K98" s="2">
-        <v>45500.583333333336</v>
+        <v>45476.479166666664</v>
       </c>
       <c r="L98" s="2">
-        <v>45500.958333333336</v>
+        <v>45476.791666666664</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>168</v>
+        <v>1515</v>
       </c>
       <c r="B99" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C99" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D99" s="1">
-        <v>45500</v>
+        <v>45476</v>
       </c>
       <c r="E99" s="2">
-        <v>45500.333333333336</v>
+        <v>45476.583333333336</v>
       </c>
       <c r="F99" s="2">
-        <v>45500.583333333336</v>
+        <v>45476.875</v>
       </c>
       <c r="G99">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H99">
-        <v>13.5</v>
+        <v>22.75</v>
       </c>
       <c r="I99" t="s">
         <v>78</v>
       </c>
       <c r="J99" s="1">
-        <v>45500</v>
+        <v>45476</v>
       </c>
       <c r="K99" s="2">
-        <v>45500.3125</v>
+        <v>45476.5625</v>
       </c>
       <c r="L99" s="2">
-        <v>45500.604166666664</v>
+        <v>45476.895833333336</v>
       </c>
     </row>
     <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B100" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C100" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D100" s="1">
         <v>45501</v>
       </c>
       <c r="E100" s="2">
-        <v>45501.5</v>
+        <v>45501.333333333336</v>
       </c>
       <c r="F100" s="2">
-        <v>45501.833333333336</v>
+        <v>45501.583333333336</v>
       </c>
       <c r="G100">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H100">
-        <v>16.25</v>
+        <v>15.25</v>
       </c>
       <c r="I100" t="s">
         <v>70</v>
@@ -4986,36 +4989,36 @@
         <v>45501</v>
       </c>
       <c r="K100" s="2">
-        <v>45501.479166666664</v>
+        <v>45501.5625</v>
       </c>
       <c r="L100" s="2">
-        <v>45501.854166666664</v>
+        <v>45501.604166666664</v>
       </c>
     </row>
     <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B101" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C101" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D101" s="1">
         <v>45501</v>
       </c>
       <c r="E101" s="2">
-        <v>45501.333333333336</v>
+        <v>45501.5</v>
       </c>
       <c r="F101" s="2">
-        <v>45501.583333333336</v>
+        <v>45501.833333333336</v>
       </c>
       <c r="G101">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H101">
-        <v>15.25</v>
+        <v>16.25</v>
       </c>
       <c r="I101" t="s">
         <v>70</v>
@@ -5024,1910 +5027,1910 @@
         <v>45501</v>
       </c>
       <c r="K101" s="2">
-        <v>45501.3125</v>
+        <v>45501.5625</v>
       </c>
       <c r="L101" s="2">
-        <v>45501.604166666664</v>
+        <v>45501.854166666664</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D102" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="E102" s="2">
-        <v>45474.333333333336</v>
+        <v>45477.25</v>
       </c>
       <c r="F102" s="2">
-        <v>45474.583333333336</v>
+        <v>45477.5</v>
       </c>
       <c r="G102">
         <v>6</v>
       </c>
       <c r="H102">
-        <v>14.75</v>
+        <v>17</v>
       </c>
       <c r="I102" t="s">
         <v>78</v>
       </c>
       <c r="J102" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="K102" s="2">
-        <v>45474.3125</v>
+        <v>45477.229166666664</v>
       </c>
       <c r="L102" s="2">
-        <v>45474.625</v>
+        <v>45477.541666666664</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>1502</v>
+        <v>1516</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C103" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D103" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="E103" s="2">
-        <v>45474.375</v>
+        <v>45477.333333333336</v>
       </c>
       <c r="F103" s="2">
-        <v>45474.75</v>
+        <v>45477.583333333336</v>
       </c>
       <c r="G103">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H103">
-        <v>28.5</v>
+        <v>15.5</v>
       </c>
       <c r="I103" t="s">
         <v>78</v>
       </c>
       <c r="J103" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="K103" s="2">
-        <v>45474.354166666664</v>
+        <v>45477.229166666664</v>
       </c>
       <c r="L103" s="2">
-        <v>45474.770833333336</v>
+        <v>45477.604166666664</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="B104" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D104" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="E104" s="2">
-        <v>45474.25</v>
+        <v>45477.375</v>
       </c>
       <c r="F104" s="2">
-        <v>45474.5</v>
+        <v>45477.708333333336</v>
       </c>
       <c r="G104">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H104">
-        <v>16.25</v>
+        <v>28</v>
       </c>
       <c r="I104" t="s">
         <v>78</v>
       </c>
       <c r="J104" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="K104" s="2">
-        <v>45474.229166666664</v>
+        <v>45477.229166666664</v>
       </c>
       <c r="L104" s="2">
-        <v>45474.541666666664</v>
+        <v>45477.729166666664</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>1504</v>
+        <v>1519</v>
       </c>
       <c r="B105" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C105" t="s">
         <v>18</v>
       </c>
       <c r="D105" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="E105" s="2">
-        <v>45474.5</v>
+        <v>45477.5</v>
       </c>
       <c r="F105" s="2">
-        <v>45474.75</v>
+        <v>45477.833333333336</v>
       </c>
       <c r="G105">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H105">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="I105" t="s">
         <v>78</v>
       </c>
       <c r="J105" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="K105" s="2">
-        <v>45474.479166666664</v>
+        <v>45477.479166666664</v>
       </c>
       <c r="L105" s="2">
-        <v>45474.791666666664</v>
+        <v>45477.854166666664</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>1505</v>
+        <v>1520</v>
       </c>
       <c r="B106" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C106" t="s">
         <v>23</v>
       </c>
       <c r="D106" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="E106" s="2">
-        <v>45474.583333333336</v>
+        <v>45477.583333333336</v>
       </c>
       <c r="F106" s="2">
-        <v>45474.916666666664</v>
+        <v>45477.916666666664</v>
       </c>
       <c r="G106">
         <v>8</v>
       </c>
       <c r="H106">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I106" t="s">
         <v>78</v>
       </c>
       <c r="J106" s="1">
-        <v>45474</v>
+        <v>45477</v>
       </c>
       <c r="K106" s="2">
-        <v>45474.5625</v>
+        <v>45477.5625</v>
       </c>
       <c r="L106" s="2">
-        <v>45474.9375</v>
+        <v>45477.9375</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>1506</v>
+        <v>1523</v>
       </c>
       <c r="B107" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C107" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D107" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="E107" s="2">
-        <v>45475.333333333336</v>
+        <v>45478.291666666664</v>
       </c>
       <c r="F107" s="2">
-        <v>45475.666666666664</v>
+        <v>45478.541666666664</v>
       </c>
       <c r="G107">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H107">
-        <v>15</v>
+        <v>16.8</v>
       </c>
       <c r="I107" t="s">
         <v>78</v>
       </c>
       <c r="J107" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="K107" s="2">
-        <v>45475.3125</v>
+        <v>45478.229166666664</v>
       </c>
       <c r="L107" s="2">
-        <v>45475.6875</v>
+        <v>45478.5625</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>1507</v>
+        <v>1521</v>
       </c>
       <c r="B108" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="C108" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D108" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="E108" s="2">
-        <v>45475.416666666664</v>
+        <v>45478.333333333336</v>
       </c>
       <c r="F108" s="2">
-        <v>45475.75</v>
+        <v>45478.666666666664</v>
       </c>
       <c r="G108">
         <v>8</v>
       </c>
       <c r="H108">
-        <v>29</v>
+        <v>15.75</v>
       </c>
       <c r="I108" t="s">
         <v>78</v>
       </c>
       <c r="J108" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="K108" s="2">
-        <v>45475.395833333336</v>
+        <v>45478.229166666664</v>
       </c>
       <c r="L108" s="2">
-        <v>45475.770833333336</v>
+        <v>45478.6875</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>1508</v>
+        <v>1522</v>
       </c>
       <c r="B109" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C109" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D109" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="E109" s="2">
-        <v>45475.208333333336</v>
+        <v>45478.375</v>
       </c>
       <c r="F109" s="2">
-        <v>45475.541666666664</v>
+        <v>45478.708333333336</v>
       </c>
       <c r="G109">
         <v>8</v>
       </c>
       <c r="H109">
-        <v>16.75</v>
+        <v>27.5</v>
       </c>
       <c r="I109" t="s">
         <v>78</v>
       </c>
       <c r="J109" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="K109" s="2">
-        <v>45475.1875</v>
+        <v>45478.354166666664</v>
       </c>
       <c r="L109" s="2">
-        <v>45475.5625</v>
+        <v>45478.729166666664</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>1509</v>
+        <v>1524</v>
       </c>
       <c r="B110" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="C110" t="s">
         <v>18</v>
       </c>
       <c r="D110" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="E110" s="2">
-        <v>45475.583333333336</v>
+        <v>45478.541666666664</v>
       </c>
       <c r="F110" s="2">
-        <v>45475.916666666664</v>
+        <v>45478.875</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110">
-        <v>17.5</v>
+        <v>17.75</v>
       </c>
       <c r="I110" t="s">
         <v>78</v>
       </c>
       <c r="J110" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="K110" s="2">
-        <v>45475.5625</v>
+        <v>45478.520833333336</v>
       </c>
       <c r="L110" s="2">
-        <v>45475.9375</v>
+        <v>45478.895833333336</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>1510</v>
+        <v>1525</v>
       </c>
       <c r="B111" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C111" t="s">
         <v>23</v>
       </c>
       <c r="D111" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="E111" s="2">
-        <v>45475.666666666664</v>
+        <v>45478.625</v>
       </c>
       <c r="F111" s="2">
-        <v>45475.958333333336</v>
+        <v>45478.916666666664</v>
       </c>
       <c r="G111">
         <v>7</v>
       </c>
       <c r="H111">
-        <v>23.5</v>
+        <v>23.25</v>
       </c>
       <c r="I111" t="s">
         <v>78</v>
       </c>
       <c r="J111" s="1">
-        <v>45475</v>
+        <v>45478</v>
       </c>
       <c r="K111" s="2">
-        <v>45475.645833333336</v>
+        <v>45478.604166666664</v>
       </c>
       <c r="L111" s="2">
-        <v>45475.979166666664</v>
+        <v>45478.9375</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>1511</v>
+        <v>1528</v>
       </c>
       <c r="B112" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D112" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="E112" s="2">
-        <v>45476.291666666664</v>
+        <v>45479.25</v>
       </c>
       <c r="F112" s="2">
-        <v>45476.541666666664</v>
+        <v>45479.5</v>
       </c>
       <c r="G112">
         <v>6</v>
       </c>
       <c r="H112">
-        <v>15.25</v>
+        <v>16.95</v>
       </c>
       <c r="I112" t="s">
         <v>78</v>
       </c>
       <c r="J112" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="K112" s="2">
-        <v>45476.270833333336</v>
+        <v>45479.229166666664</v>
       </c>
       <c r="L112" s="2">
-        <v>45476.5625</v>
+        <v>45479.541666666664</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>1512</v>
+        <v>1526</v>
       </c>
       <c r="B113" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="C113" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D113" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="E113" s="2">
-        <v>45476.375</v>
+        <v>45479.291666666664</v>
       </c>
       <c r="F113" s="2">
-        <v>45476.75</v>
+        <v>45479.625</v>
       </c>
       <c r="G113">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H113">
-        <v>27.75</v>
+        <v>15.95</v>
       </c>
       <c r="I113" t="s">
         <v>78</v>
       </c>
       <c r="J113" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="K113" s="2">
-        <v>45476.354166666664</v>
+        <v>45479.229166666664</v>
       </c>
       <c r="L113" s="2">
-        <v>45476.770833333336</v>
+        <v>45479.645833333336</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>1513</v>
+        <v>1527</v>
       </c>
       <c r="B114" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D114" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="E114" s="2">
-        <v>45476.25</v>
+        <v>45479.375</v>
       </c>
       <c r="F114" s="2">
-        <v>45476.5</v>
+        <v>45479.708333333336</v>
       </c>
       <c r="G114">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H114">
-        <v>16.5</v>
+        <v>28.25</v>
       </c>
       <c r="I114" t="s">
         <v>78</v>
       </c>
       <c r="J114" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="K114" s="2">
-        <v>45476.229166666664</v>
+        <v>45479.354166666664</v>
       </c>
       <c r="L114" s="2">
-        <v>45476.541666666664</v>
+        <v>45479.729166666664</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>1514</v>
+        <v>1529</v>
       </c>
       <c r="B115" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C115" t="s">
         <v>18</v>
       </c>
       <c r="D115" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="E115" s="2">
-        <v>45476.5</v>
+        <v>45479.541666666664</v>
       </c>
       <c r="F115" s="2">
-        <v>45476.75</v>
+        <v>45479.875</v>
       </c>
       <c r="G115">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H115">
-        <v>18</v>
+        <v>18.25</v>
       </c>
       <c r="I115" t="s">
         <v>78</v>
       </c>
       <c r="J115" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="K115" s="2">
-        <v>45476.479166666664</v>
+        <v>45479.520833333336</v>
       </c>
       <c r="L115" s="2">
-        <v>45476.791666666664</v>
+        <v>45479.895833333336</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>1515</v>
+        <v>1530</v>
       </c>
       <c r="B116" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C116" t="s">
         <v>23</v>
       </c>
       <c r="D116" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="E116" s="2">
-        <v>45476.583333333336</v>
+        <v>45479.625</v>
       </c>
       <c r="F116" s="2">
-        <v>45476.875</v>
+        <v>45479.916666666664</v>
       </c>
       <c r="G116">
         <v>7</v>
       </c>
       <c r="H116">
-        <v>22.75</v>
+        <v>22.95</v>
       </c>
       <c r="I116" t="s">
         <v>78</v>
       </c>
       <c r="J116" s="1">
-        <v>45476</v>
+        <v>45479</v>
       </c>
       <c r="K116" s="2">
-        <v>45476.5625</v>
+        <v>45479.604166666664</v>
       </c>
       <c r="L116" s="2">
-        <v>45476.895833333336</v>
+        <v>45479.9375</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>1516</v>
+        <v>1533</v>
       </c>
       <c r="B117" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D117" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="E117" s="2">
-        <v>45477.333333333336</v>
+        <v>45480.25</v>
       </c>
       <c r="F117" s="2">
-        <v>45477.583333333336</v>
+        <v>45480.5</v>
       </c>
       <c r="G117">
         <v>6</v>
       </c>
       <c r="H117">
-        <v>15.5</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="I117" t="s">
         <v>78</v>
       </c>
       <c r="J117" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="K117" s="2">
-        <v>45477.3125</v>
+        <v>45480.229166666664</v>
       </c>
       <c r="L117" s="2">
-        <v>45477.604166666664</v>
+        <v>45480.541666666664</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>1517</v>
+        <v>1531</v>
       </c>
       <c r="B118" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C118" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D118" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="E118" s="2">
-        <v>45477.375</v>
+        <v>45480.333333333336</v>
       </c>
       <c r="F118" s="2">
-        <v>45477.708333333336</v>
+        <v>45480.583333333336</v>
       </c>
       <c r="G118">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H118">
-        <v>28</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="I118" t="s">
         <v>78</v>
       </c>
       <c r="J118" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="K118" s="2">
-        <v>45477.354166666664</v>
+        <v>45480.3125</v>
       </c>
       <c r="L118" s="2">
-        <v>45477.729166666664</v>
+        <v>45480.604166666664</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>1518</v>
+        <v>1532</v>
       </c>
       <c r="B119" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C119" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D119" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="E119" s="2">
-        <v>45477.25</v>
+        <v>45480.375</v>
       </c>
       <c r="F119" s="2">
-        <v>45477.5</v>
+        <v>45480.708333333336</v>
       </c>
       <c r="G119">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H119">
-        <v>17</v>
+        <v>29.25</v>
       </c>
       <c r="I119" t="s">
         <v>78</v>
       </c>
       <c r="J119" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="K119" s="2">
-        <v>45477.229166666664</v>
+        <v>45480.354166666664</v>
       </c>
       <c r="L119" s="2">
-        <v>45477.541666666664</v>
+        <v>45480.729166666664</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>1519</v>
+        <v>128</v>
       </c>
       <c r="B120" t="s">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="C120" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D120" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="E120" s="2">
-        <v>45477.5</v>
+        <v>45480.416666666664</v>
       </c>
       <c r="F120" s="2">
-        <v>45477.833333333336</v>
+        <v>45480.75</v>
       </c>
       <c r="G120">
         <v>8</v>
       </c>
       <c r="H120">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="I120" t="s">
         <v>78</v>
       </c>
       <c r="J120" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="K120" s="2">
-        <v>45477.479166666664</v>
+        <v>45480.375</v>
       </c>
       <c r="L120" s="2">
-        <v>45477.854166666664</v>
+        <v>45480.791666666664</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>1520</v>
+        <v>1534</v>
       </c>
       <c r="B121" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C121" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D121" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="E121" s="2">
-        <v>45477.583333333336</v>
+        <v>45480.541666666664</v>
       </c>
       <c r="F121" s="2">
-        <v>45477.916666666664</v>
+        <v>45480.875</v>
       </c>
       <c r="G121">
         <v>8</v>
       </c>
       <c r="H121">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I121" t="s">
         <v>78</v>
       </c>
       <c r="J121" s="1">
-        <v>45477</v>
+        <v>45480</v>
       </c>
       <c r="K121" s="2">
-        <v>45477.5625</v>
+        <v>45480.520833333336</v>
       </c>
       <c r="L121" s="2">
-        <v>45477.9375</v>
+        <v>45480.895833333336</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>1521</v>
+        <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="C122" t="s">
         <v>13</v>
       </c>
       <c r="D122" s="1">
-        <v>45478</v>
+        <v>45480</v>
       </c>
       <c r="E122" s="2">
-        <v>45478.333333333336</v>
+        <v>45480.625</v>
       </c>
       <c r="F122" s="2">
-        <v>45478.666666666664</v>
+        <v>45480.875</v>
       </c>
       <c r="G122">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H122">
-        <v>15.75</v>
+        <v>15</v>
       </c>
       <c r="I122" t="s">
         <v>78</v>
       </c>
       <c r="J122" s="1">
-        <v>45478</v>
+        <v>45480</v>
       </c>
       <c r="K122" s="2">
-        <v>45478.3125</v>
+        <v>45480.583333333336</v>
       </c>
       <c r="L122" s="2">
-        <v>45478.6875</v>
+        <v>45480.916666666664</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>1522</v>
+        <v>1535</v>
       </c>
       <c r="B123" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C123" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D123" s="1">
-        <v>45478</v>
+        <v>45480</v>
       </c>
       <c r="E123" s="2">
-        <v>45478.375</v>
+        <v>45480.625</v>
       </c>
       <c r="F123" s="2">
-        <v>45478.708333333336</v>
+        <v>45480.916666666664</v>
       </c>
       <c r="G123">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H123">
-        <v>27.5</v>
+        <v>24</v>
       </c>
       <c r="I123" t="s">
         <v>78</v>
       </c>
       <c r="J123" s="1">
-        <v>45478</v>
+        <v>45480</v>
       </c>
       <c r="K123" s="2">
-        <v>45478.354166666664</v>
+        <v>45480.604166666664</v>
       </c>
       <c r="L123" s="2">
-        <v>45478.729166666664</v>
+        <v>45480.9375</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>1523</v>
+        <v>1538</v>
       </c>
       <c r="B124" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="C124" t="s">
         <v>20</v>
       </c>
       <c r="D124" s="1">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="E124" s="2">
-        <v>45478.291666666664</v>
+        <v>45481.25</v>
       </c>
       <c r="F124" s="2">
-        <v>45478.541666666664</v>
+        <v>45481.5</v>
       </c>
       <c r="G124">
         <v>6</v>
       </c>
       <c r="H124">
-        <v>16.8</v>
+        <v>17.25</v>
       </c>
       <c r="I124" t="s">
         <v>78</v>
       </c>
       <c r="J124" s="1">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="K124" s="2">
-        <v>45478.270833333336</v>
+        <v>45481.229166666664</v>
       </c>
       <c r="L124" s="2">
-        <v>45478.5625</v>
+        <v>45481.541666666664</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>1524</v>
+        <v>1536</v>
       </c>
       <c r="B125" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C125" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D125" s="1">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="E125" s="2">
-        <v>45478.541666666664</v>
+        <v>45481.333333333336</v>
       </c>
       <c r="F125" s="2">
-        <v>45478.875</v>
+        <v>45481.583333333336</v>
       </c>
       <c r="G125">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H125">
-        <v>17.75</v>
+        <v>16.25</v>
       </c>
       <c r="I125" t="s">
         <v>78</v>
       </c>
       <c r="J125" s="1">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="K125" s="2">
-        <v>45478.520833333336</v>
+        <v>45481.229166666664</v>
       </c>
       <c r="L125" s="2">
-        <v>45478.895833333336</v>
+        <v>45481.604166666664</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>1525</v>
+        <v>1537</v>
       </c>
       <c r="B126" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C126" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D126" s="1">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="E126" s="2">
-        <v>45478.625</v>
+        <v>45481.375</v>
       </c>
       <c r="F126" s="2">
-        <v>45478.916666666664</v>
+        <v>45481.708333333336</v>
       </c>
       <c r="G126">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H126">
-        <v>23.25</v>
+        <v>29.75</v>
       </c>
       <c r="I126" t="s">
         <v>78</v>
       </c>
       <c r="J126" s="1">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="K126" s="2">
-        <v>45478.604166666664</v>
+        <v>45481.229166666664</v>
       </c>
       <c r="L126" s="2">
-        <v>45478.9375</v>
+        <v>45481.729166666664</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>1526</v>
+        <v>1539</v>
       </c>
       <c r="B127" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C127" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D127" s="1">
-        <v>45479</v>
+        <v>45481</v>
       </c>
       <c r="E127" s="2">
-        <v>45479.291666666664</v>
+        <v>45481.5</v>
       </c>
       <c r="F127" s="2">
-        <v>45479.625</v>
+        <v>45481.75</v>
       </c>
       <c r="G127">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H127">
-        <v>15.95</v>
+        <v>18.25</v>
       </c>
       <c r="I127" t="s">
         <v>78</v>
       </c>
       <c r="J127" s="1">
-        <v>45479</v>
+        <v>45481</v>
       </c>
       <c r="K127" s="2">
-        <v>45479.270833333336</v>
+        <v>45481.479166666664</v>
       </c>
       <c r="L127" s="2">
-        <v>45479.645833333336</v>
+        <v>45481.791666666664</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>1527</v>
+        <v>1540</v>
       </c>
       <c r="B128" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C128" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D128" s="1">
-        <v>45479</v>
+        <v>45481</v>
       </c>
       <c r="E128" s="2">
-        <v>45479.375</v>
+        <v>45481.583333333336</v>
       </c>
       <c r="F128" s="2">
-        <v>45479.708333333336</v>
+        <v>45481.875</v>
       </c>
       <c r="G128">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H128">
-        <v>28.25</v>
+        <v>24.25</v>
       </c>
       <c r="I128" t="s">
         <v>78</v>
       </c>
       <c r="J128" s="1">
-        <v>45479</v>
+        <v>45481</v>
       </c>
       <c r="K128" s="2">
-        <v>45479.354166666664</v>
+        <v>45481.5625</v>
       </c>
       <c r="L128" s="2">
-        <v>45479.729166666664</v>
+        <v>45481.895833333336</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>1528</v>
+        <v>1543</v>
       </c>
       <c r="B129" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="C129" t="s">
         <v>20</v>
       </c>
       <c r="D129" s="1">
-        <v>45479</v>
+        <v>45482</v>
       </c>
       <c r="E129" s="2">
-        <v>45479.25</v>
+        <v>45482.25</v>
       </c>
       <c r="F129" s="2">
-        <v>45479.5</v>
+        <v>45482.5</v>
       </c>
       <c r="G129">
         <v>6</v>
       </c>
       <c r="H129">
-        <v>16.95</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I129" t="s">
         <v>78</v>
       </c>
       <c r="J129" s="1">
-        <v>45479</v>
+        <v>45482</v>
       </c>
       <c r="K129" s="2">
-        <v>45479.229166666664</v>
+        <v>45482.229166666664</v>
       </c>
       <c r="L129" s="2">
-        <v>45479.541666666664</v>
+        <v>45482.541666666664</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>1529</v>
+        <v>1541</v>
       </c>
       <c r="B130" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C130" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D130" s="1">
-        <v>45479</v>
+        <v>45482</v>
       </c>
       <c r="E130" s="2">
-        <v>45479.541666666664</v>
+        <v>45482.333333333336</v>
       </c>
       <c r="F130" s="2">
-        <v>45479.875</v>
+        <v>45482.583333333336</v>
       </c>
       <c r="G130">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H130">
-        <v>18.25</v>
+        <v>16.5</v>
       </c>
       <c r="I130" t="s">
         <v>78</v>
       </c>
       <c r="J130" s="1">
-        <v>45479</v>
+        <v>45482</v>
       </c>
       <c r="K130" s="2">
-        <v>45479.520833333336</v>
+        <v>45482.229166666664</v>
       </c>
       <c r="L130" s="2">
-        <v>45479.895833333336</v>
+        <v>45482.604166666664</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>1530</v>
+        <v>1542</v>
       </c>
       <c r="B131" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C131" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D131" s="1">
-        <v>45479</v>
+        <v>45482</v>
       </c>
       <c r="E131" s="2">
-        <v>45479.625</v>
+        <v>45482.375</v>
       </c>
       <c r="F131" s="2">
-        <v>45479.916666666664</v>
+        <v>45482.708333333336</v>
       </c>
       <c r="G131">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H131">
-        <v>22.95</v>
+        <v>30</v>
       </c>
       <c r="I131" t="s">
         <v>78</v>
       </c>
       <c r="J131" s="1">
-        <v>45479</v>
+        <v>45482</v>
       </c>
       <c r="K131" s="2">
-        <v>45479.604166666664</v>
+        <v>45482.229166666664</v>
       </c>
       <c r="L131" s="2">
-        <v>45479.9375</v>
+        <v>45482.729166666664</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>1531</v>
+        <v>1544</v>
       </c>
       <c r="B132" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C132" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D132" s="1">
-        <v>45480</v>
+        <v>45482</v>
       </c>
       <c r="E132" s="2">
-        <v>45480.333333333336</v>
+        <v>45482.5</v>
       </c>
       <c r="F132" s="2">
-        <v>45480.583333333336</v>
+        <v>45482.75</v>
       </c>
       <c r="G132">
         <v>6</v>
       </c>
       <c r="H132">
-        <v>16.100000000000001</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="I132" t="s">
         <v>78</v>
       </c>
       <c r="J132" s="1">
-        <v>45480</v>
+        <v>45482</v>
       </c>
       <c r="K132" s="2">
-        <v>45480.3125</v>
+        <v>45482.479166666664</v>
       </c>
       <c r="L132" s="2">
-        <v>45480.604166666664</v>
+        <v>45482.791666666664</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>1532</v>
+        <v>1545</v>
       </c>
       <c r="B133" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C133" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D133" s="1">
-        <v>45480</v>
+        <v>45482</v>
       </c>
       <c r="E133" s="2">
-        <v>45480.375</v>
+        <v>45482.625</v>
       </c>
       <c r="F133" s="2">
-        <v>45480.708333333336</v>
+        <v>45482.916666666664</v>
       </c>
       <c r="G133">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H133">
-        <v>29.25</v>
+        <v>24.5</v>
       </c>
       <c r="I133" t="s">
         <v>78</v>
       </c>
       <c r="J133" s="1">
-        <v>45480</v>
+        <v>45482</v>
       </c>
       <c r="K133" s="2">
-        <v>45480.354166666664</v>
+        <v>45482.604166666664</v>
       </c>
       <c r="L133" s="2">
-        <v>45480.729166666664</v>
+        <v>45482.9375</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>1533</v>
+        <v>1548</v>
       </c>
       <c r="B134" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C134" t="s">
         <v>20</v>
       </c>
       <c r="D134" s="1">
-        <v>45480</v>
+        <v>45483</v>
       </c>
       <c r="E134" s="2">
-        <v>45480.25</v>
+        <v>45483.25</v>
       </c>
       <c r="F134" s="2">
-        <v>45480.5</v>
+        <v>45483.5</v>
       </c>
       <c r="G134">
         <v>6</v>
       </c>
       <c r="H134">
-        <v>17.100000000000001</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="I134" t="s">
         <v>78</v>
       </c>
       <c r="J134" s="1">
-        <v>45480</v>
+        <v>45483</v>
       </c>
       <c r="K134" s="2">
-        <v>45480.229166666664</v>
+        <v>45483.229166666664</v>
       </c>
       <c r="L134" s="2">
-        <v>45480.541666666664</v>
+        <v>45483.541666666664</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>1534</v>
+        <v>1546</v>
       </c>
       <c r="B135" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C135" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D135" s="1">
-        <v>45480</v>
+        <v>45483</v>
       </c>
       <c r="E135" s="2">
-        <v>45480.541666666664</v>
+        <v>45483.333333333336</v>
       </c>
       <c r="F135" s="2">
-        <v>45480.875</v>
+        <v>45483.583333333336</v>
       </c>
       <c r="G135">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H135">
-        <v>19</v>
+        <v>16.75</v>
       </c>
       <c r="I135" t="s">
         <v>78</v>
       </c>
       <c r="J135" s="1">
-        <v>45480</v>
+        <v>45483</v>
       </c>
       <c r="K135" s="2">
-        <v>45480.520833333336</v>
+        <v>45483.229166666664</v>
       </c>
       <c r="L135" s="2">
-        <v>45480.895833333336</v>
+        <v>45483.604166666664</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>1535</v>
+        <v>1547</v>
       </c>
       <c r="B136" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C136" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D136" s="1">
-        <v>45480</v>
+        <v>45483</v>
       </c>
       <c r="E136" s="2">
-        <v>45480.625</v>
+        <v>45483.375</v>
       </c>
       <c r="F136" s="2">
-        <v>45480.916666666664</v>
+        <v>45483.708333333336</v>
       </c>
       <c r="G136">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H136">
-        <v>24</v>
+        <v>21.5</v>
       </c>
       <c r="I136" t="s">
         <v>78</v>
       </c>
       <c r="J136" s="1">
-        <v>45480</v>
+        <v>45483</v>
       </c>
       <c r="K136" s="2">
-        <v>45480.604166666664</v>
+        <v>45483.229166666664</v>
       </c>
       <c r="L136" s="2">
-        <v>45480.9375</v>
+        <v>45483.729166666664</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>1536</v>
+        <v>1549</v>
       </c>
       <c r="B137" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C137" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D137" s="1">
-        <v>45481</v>
+        <v>45483</v>
       </c>
       <c r="E137" s="2">
-        <v>45481.333333333336</v>
+        <v>45483.5</v>
       </c>
       <c r="F137" s="2">
-        <v>45481.583333333336</v>
+        <v>45483.75</v>
       </c>
       <c r="G137">
         <v>6</v>
       </c>
       <c r="H137">
-        <v>16.25</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="I137" t="s">
         <v>78</v>
       </c>
       <c r="J137" s="1">
-        <v>45481</v>
+        <v>45483</v>
       </c>
       <c r="K137" s="2">
-        <v>45481.3125</v>
+        <v>45483.479166666664</v>
       </c>
       <c r="L137" s="2">
-        <v>45481.604166666664</v>
+        <v>45483.791666666664</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>1537</v>
+        <v>133</v>
       </c>
       <c r="B138" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="C138" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D138" s="1">
-        <v>45481</v>
+        <v>45483</v>
       </c>
       <c r="E138" s="2">
-        <v>45481.375</v>
+        <v>45483.583333333336</v>
       </c>
       <c r="F138" s="2">
-        <v>45481.708333333336</v>
+        <v>45483.833333333336</v>
       </c>
       <c r="G138">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H138">
-        <v>29.75</v>
+        <v>13.25</v>
       </c>
       <c r="I138" t="s">
         <v>78</v>
       </c>
       <c r="J138" s="1">
-        <v>45481</v>
+        <v>45483</v>
       </c>
       <c r="K138" s="2">
-        <v>45481.354166666664</v>
+        <v>45483.541666666664</v>
       </c>
       <c r="L138" s="2">
-        <v>45481.729166666664</v>
+        <v>45483.875</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>1538</v>
+        <v>1550</v>
       </c>
       <c r="B139" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C139" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D139" s="1">
-        <v>45481</v>
+        <v>45483</v>
       </c>
       <c r="E139" s="2">
-        <v>45481.25</v>
+        <v>45483.583333333336</v>
       </c>
       <c r="F139" s="2">
-        <v>45481.5</v>
+        <v>45483.875</v>
       </c>
       <c r="G139">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H139">
-        <v>17.25</v>
+        <v>25</v>
       </c>
       <c r="I139" t="s">
         <v>78</v>
       </c>
       <c r="J139" s="1">
-        <v>45481</v>
+        <v>45483</v>
       </c>
       <c r="K139" s="2">
-        <v>45481.229166666664</v>
+        <v>45483.5625</v>
       </c>
       <c r="L139" s="2">
-        <v>45481.541666666664</v>
+        <v>45483.895833333336</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>1539</v>
+        <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
       </c>
       <c r="D140" s="1">
-        <v>45481</v>
+        <v>45484</v>
       </c>
       <c r="E140" s="2">
-        <v>45481.5</v>
+        <v>45484.666666666664</v>
       </c>
       <c r="F140" s="2">
-        <v>45481.75</v>
+        <v>45484.916666666664</v>
       </c>
       <c r="G140">
         <v>6</v>
       </c>
       <c r="H140">
-        <v>18.25</v>
+        <v>16.5</v>
       </c>
       <c r="I140" t="s">
         <v>78</v>
       </c>
       <c r="J140" s="1">
-        <v>45481</v>
+        <v>45484</v>
       </c>
       <c r="K140" s="2">
-        <v>45481.479166666664</v>
+        <v>45484.625</v>
       </c>
       <c r="L140" s="2">
-        <v>45481.791666666664</v>
+        <v>45484.958333333336</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>1540</v>
+        <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="C141" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D141" s="1">
-        <v>45481</v>
+        <v>45486</v>
       </c>
       <c r="E141" s="2">
-        <v>45481.583333333336</v>
+        <v>45486.375</v>
       </c>
       <c r="F141" s="2">
-        <v>45481.875</v>
+        <v>45486.708333333336</v>
       </c>
       <c r="G141">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H141">
-        <v>24.25</v>
+        <v>16.75</v>
       </c>
       <c r="I141" t="s">
         <v>78</v>
       </c>
       <c r="J141" s="1">
-        <v>45481</v>
+        <v>45486</v>
       </c>
       <c r="K141" s="2">
-        <v>45481.5625</v>
+        <v>45486.25</v>
       </c>
       <c r="L141" s="2">
-        <v>45481.895833333336</v>
+        <v>45486.729166666664</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>1541</v>
+        <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>162</v>
+        <v>93</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D142" s="1">
-        <v>45482</v>
+        <v>45487</v>
       </c>
       <c r="E142" s="2">
-        <v>45482.333333333336</v>
+        <v>45487.333333333336</v>
       </c>
       <c r="F142" s="2">
-        <v>45482.583333333336</v>
+        <v>45487.583333333336</v>
       </c>
       <c r="G142">
         <v>6</v>
       </c>
       <c r="H142">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="I142" t="s">
         <v>78</v>
       </c>
       <c r="J142" s="1">
-        <v>45482</v>
+        <v>45487</v>
       </c>
       <c r="K142" s="2">
-        <v>45482.3125</v>
+        <v>45487.229166666664</v>
       </c>
       <c r="L142" s="2">
-        <v>45482.604166666664</v>
+        <v>45487.604166666664</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>1542</v>
+        <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="C143" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D143" s="1">
-        <v>45482</v>
+        <v>45488</v>
       </c>
       <c r="E143" s="2">
-        <v>45482.375</v>
+        <v>45488.583333333336</v>
       </c>
       <c r="F143" s="2">
-        <v>45482.708333333336</v>
+        <v>45488.916666666664</v>
       </c>
       <c r="G143">
         <v>8</v>
       </c>
       <c r="H143">
-        <v>30</v>
+        <v>21.75</v>
       </c>
       <c r="I143" t="s">
         <v>78</v>
       </c>
       <c r="J143" s="1">
-        <v>45482</v>
+        <v>45488</v>
       </c>
       <c r="K143" s="2">
-        <v>45482.354166666664</v>
+        <v>45488.541666666664</v>
       </c>
       <c r="L143" s="2">
-        <v>45482.729166666664</v>
+        <v>45488.958333333336</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>1543</v>
+        <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="C144" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D144" s="1">
-        <v>45482</v>
+        <v>45489</v>
       </c>
       <c r="E144" s="2">
-        <v>45482.25</v>
+        <v>45489.458333333336</v>
       </c>
       <c r="F144" s="2">
-        <v>45482.5</v>
+        <v>45489.666666666664</v>
       </c>
       <c r="G144">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H144">
-        <v>17.399999999999999</v>
+        <v>14</v>
       </c>
       <c r="I144" t="s">
         <v>78</v>
       </c>
       <c r="J144" s="1">
-        <v>45482</v>
+        <v>45489</v>
       </c>
       <c r="K144" s="2">
-        <v>45482.229166666664</v>
+        <v>45489.4375</v>
       </c>
       <c r="L144" s="2">
-        <v>45482.541666666664</v>
+        <v>45489.6875</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>1544</v>
+        <v>151</v>
       </c>
       <c r="B145" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="C145" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D145" s="1">
-        <v>45482</v>
+        <v>45492</v>
       </c>
       <c r="E145" s="2">
-        <v>45482.5</v>
+        <v>45492.375</v>
       </c>
       <c r="F145" s="2">
-        <v>45482.75</v>
+        <v>45492.625</v>
       </c>
       <c r="G145">
         <v>6</v>
       </c>
       <c r="H145">
-        <v>18.399999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="I145" t="s">
         <v>78</v>
       </c>
       <c r="J145" s="1">
-        <v>45482</v>
+        <v>45492</v>
       </c>
       <c r="K145" s="2">
-        <v>45482.479166666664</v>
+        <v>45492.354166666664</v>
       </c>
       <c r="L145" s="2">
-        <v>45482.791666666664</v>
+        <v>45492.666666666664</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>1545</v>
+        <v>152</v>
       </c>
       <c r="B146" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="C146" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D146" s="1">
-        <v>45482</v>
+        <v>45492</v>
       </c>
       <c r="E146" s="2">
-        <v>45482.625</v>
+        <v>45492.541666666664</v>
       </c>
       <c r="F146" s="2">
-        <v>45482.916666666664</v>
+        <v>45492.875</v>
       </c>
       <c r="G146">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H146">
-        <v>24.5</v>
+        <v>16.75</v>
       </c>
       <c r="I146" t="s">
         <v>78</v>
       </c>
       <c r="J146" s="1">
-        <v>45482</v>
+        <v>45492</v>
       </c>
       <c r="K146" s="2">
-        <v>45482.604166666664</v>
+        <v>45492.520833333336</v>
       </c>
       <c r="L146" s="2">
-        <v>45482.9375</v>
+        <v>45492.895833333336</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>1546</v>
+        <v>157</v>
       </c>
       <c r="B147" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="C147" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D147" s="1">
-        <v>45483</v>
+        <v>45495</v>
       </c>
       <c r="E147" s="2">
-        <v>45483.333333333336</v>
+        <v>45495.354166666664</v>
       </c>
       <c r="F147" s="2">
-        <v>45483.583333333336</v>
+        <v>45495.604166666664</v>
       </c>
       <c r="G147">
         <v>6</v>
       </c>
       <c r="H147">
-        <v>16.75</v>
+        <v>13.75</v>
       </c>
       <c r="I147" t="s">
         <v>78</v>
       </c>
       <c r="J147" s="1">
-        <v>45483</v>
+        <v>45495</v>
       </c>
       <c r="K147" s="2">
-        <v>45483.3125</v>
+        <v>45495.333333333336</v>
       </c>
       <c r="L147" s="2">
-        <v>45483.604166666664</v>
+        <v>45495.625</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>1547</v>
+        <v>158</v>
       </c>
       <c r="B148" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="C148" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D148" s="1">
-        <v>45483</v>
+        <v>45495</v>
       </c>
       <c r="E148" s="2">
-        <v>45483.375</v>
+        <v>45495.541666666664</v>
       </c>
       <c r="F148" s="2">
-        <v>45483.708333333336</v>
+        <v>45495.791666666664</v>
       </c>
       <c r="G148">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H148">
-        <v>21.5</v>
+        <v>15.5</v>
       </c>
       <c r="I148" t="s">
         <v>78</v>
       </c>
       <c r="J148" s="1">
-        <v>45483</v>
+        <v>45495</v>
       </c>
       <c r="K148" s="2">
-        <v>45483.354166666664</v>
+        <v>45495.520833333336</v>
       </c>
       <c r="L148" s="2">
-        <v>45483.729166666664</v>
+        <v>45495.8125</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>1548</v>
+        <v>162</v>
       </c>
       <c r="B149" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="C149" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D149" s="1">
-        <v>45483</v>
+        <v>45497</v>
       </c>
       <c r="E149" s="2">
-        <v>45483.25</v>
+        <v>45497.375</v>
       </c>
       <c r="F149" s="2">
-        <v>45483.5</v>
+        <v>45497.625</v>
       </c>
       <c r="G149">
         <v>6</v>
       </c>
       <c r="H149">
-        <v>17.600000000000001</v>
+        <v>15.75</v>
       </c>
       <c r="I149" t="s">
         <v>78</v>
       </c>
       <c r="J149" s="1">
-        <v>45483</v>
+        <v>45497</v>
       </c>
       <c r="K149" s="2">
-        <v>45483.229166666664</v>
+        <v>45497.354166666664</v>
       </c>
       <c r="L149" s="2">
-        <v>45483.541666666664</v>
+        <v>45497.645833333336</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>1549</v>
+        <v>168</v>
       </c>
       <c r="B150" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="C150" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D150" s="1">
-        <v>45483</v>
+        <v>45500</v>
       </c>
       <c r="E150" s="2">
-        <v>45483.5</v>
+        <v>45500.333333333336</v>
       </c>
       <c r="F150" s="2">
-        <v>45483.75</v>
+        <v>45500.583333333336</v>
       </c>
       <c r="G150">
         <v>6</v>
       </c>
       <c r="H150">
-        <v>18.600000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="I150" t="s">
         <v>78</v>
       </c>
       <c r="J150" s="1">
-        <v>45483</v>
+        <v>45500</v>
       </c>
       <c r="K150" s="2">
-        <v>45483.479166666664</v>
+        <v>45500.229166666664</v>
       </c>
       <c r="L150" s="2">
-        <v>45483.791666666664</v>
+        <v>45500.604166666664</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>1550</v>
+        <v>167</v>
       </c>
       <c r="B151" t="s">
-        <v>171</v>
+        <v>118</v>
       </c>
       <c r="C151" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D151" s="1">
-        <v>45483</v>
+        <v>45500</v>
       </c>
       <c r="E151" s="2">
-        <v>45483.583333333336</v>
+        <v>45500.625</v>
       </c>
       <c r="F151" s="2">
-        <v>45483.875</v>
+        <v>45500.916666666664</v>
       </c>
       <c r="G151">
         <v>7</v>
       </c>
       <c r="H151">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I151" t="s">
         <v>78</v>
       </c>
       <c r="J151" s="1">
-        <v>45483</v>
+        <v>45500</v>
       </c>
       <c r="K151" s="2">
-        <v>45483.5625</v>
+        <v>45500.583333333336</v>
       </c>
       <c r="L151" s="2">
-        <v>45483.895833333336</v>
+        <v>45500.958333333336</v>
       </c>
     </row>
     <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
